--- a/reconcile/storage/output/ongoing/ongoing_total_q.xlsx
+++ b/reconcile/storage/output/ongoing/ongoing_total_q.xlsx
@@ -511,7 +511,7 @@
         <v>44286</v>
       </c>
       <c r="B2" t="n">
-        <v>975632004.7927805</v>
+        <v>975632004.4959705</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -532,10 +532,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>11550678.60236789</v>
+        <v>11550679</v>
       </c>
       <c r="J2" t="n">
-        <v>221758048.108058</v>
+        <v>230695539.1742424</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -544,7 +544,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1332561601.961032</v>
+        <v>1089716321.471411</v>
       </c>
       <c r="N2" t="n">
         <v>46959256.25</v>
@@ -555,7 +555,7 @@
         <v>44377</v>
       </c>
       <c r="B3" t="n">
-        <v>1187824424.748234</v>
+        <v>1203405117.125172</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -564,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>102267744.5816617</v>
+        <v>102267744.5833333</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -579,7 +579,7 @@
         <v>14750000</v>
       </c>
       <c r="J3" t="n">
-        <v>312022620.233058</v>
+        <v>320960111.2992424</v>
       </c>
       <c r="K3" t="n">
         <v>2266666.666666667</v>
@@ -588,10 +588,10 @@
         <v>13750000</v>
       </c>
       <c r="M3" t="n">
-        <v>1337561601.961032</v>
+        <v>1171530676.554744</v>
       </c>
       <c r="N3" t="n">
-        <v>39657062.34711446</v>
+        <v>39657062.33333334</v>
       </c>
     </row>
     <row r="4">
@@ -599,7 +599,7 @@
         <v>44469</v>
       </c>
       <c r="B4" t="n">
-        <v>1180193591.414901</v>
+        <v>1226935668.625172</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -608,7 +608,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>21961616.87249255</v>
+        <v>21961616.875</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -623,7 +623,7 @@
         <v>23625000</v>
       </c>
       <c r="J4" t="n">
-        <v>278045483.0068675</v>
+        <v>286982974.0730519</v>
       </c>
       <c r="K4" t="n">
         <v>3400000</v>
@@ -632,10 +632,10 @@
         <v>20625000</v>
       </c>
       <c r="M4" t="n">
-        <v>1335842851.961032</v>
+        <v>1323440636.721411</v>
       </c>
       <c r="N4" t="n">
-        <v>59943623.85509342</v>
+        <v>59943623.83333334</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>44561</v>
       </c>
       <c r="B5" t="n">
-        <v>1179439701.548401</v>
+        <v>1229672233.833505</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -652,7 +652,7 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>206099263.4460593</v>
+        <v>206099263.4583333</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -667,7 +667,7 @@
         <v>24895833.33333334</v>
       </c>
       <c r="J5" t="n">
-        <v>691666798881917.2</v>
+        <v>141221908.3641775</v>
       </c>
       <c r="K5" t="n">
         <v>3400000</v>
@@ -676,10 +676,10 @@
         <v>20625000</v>
       </c>
       <c r="M5" t="n">
-        <v>1340376843.189103</v>
+        <v>1193037557.011266</v>
       </c>
       <c r="N5" t="n">
-        <v>76853757.0493428</v>
+        <v>76853757</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>44651</v>
       </c>
       <c r="B6" t="n">
-        <v>829549477.1894264</v>
+        <v>879782009.4745311</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>570251677.3120422</v>
+        <v>570251677.3333334</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -711,7 +711,7 @@
         <v>26256250</v>
       </c>
       <c r="J6" t="n">
-        <v>1037500279595780</v>
+        <v>288637021.4285715</v>
       </c>
       <c r="K6" t="n">
         <v>3400000</v>
@@ -720,10 +720,10 @@
         <v>20625000</v>
       </c>
       <c r="M6" t="n">
-        <v>1006883253.445513</v>
+        <v>1651606397.590976</v>
       </c>
       <c r="N6" t="n">
-        <v>89171252.56416465</v>
+        <v>89171252.5</v>
       </c>
     </row>
     <row r="7">
@@ -731,7 +731,7 @@
         <v>44742</v>
       </c>
       <c r="B7" t="n">
-        <v>1108494990.009939</v>
+        <v>1158727522.295044</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -740,7 +740,7 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>618323418.7497417</v>
+        <v>618323418.75</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -755,7 +755,7 @@
         <v>26256250</v>
       </c>
       <c r="J7" t="n">
-        <v>1037500285354375</v>
+        <v>294395616.4285714</v>
       </c>
       <c r="K7" t="n">
         <v>3400000</v>
@@ -764,10 +764,10 @@
         <v>20625000</v>
       </c>
       <c r="M7" t="n">
-        <v>1074469791.907051</v>
+        <v>1219257038.616617</v>
       </c>
       <c r="N7" t="n">
-        <v>75513700.48083133</v>
+        <v>75513700.41666667</v>
       </c>
     </row>
     <row r="8">
@@ -775,7 +775,7 @@
         <v>44834</v>
       </c>
       <c r="B8" t="n">
-        <v>1232342930.291425</v>
+        <v>1282575462.589161</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -784,7 +784,7 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>571323421.1478232</v>
+        <v>573763466.75</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>26256250</v>
       </c>
       <c r="J8" t="n">
-        <v>1037500743553316</v>
+        <v>752594557.5535715</v>
       </c>
       <c r="K8" t="n">
         <v>3400000</v>
@@ -808,10 +808,10 @@
         <v>20625000</v>
       </c>
       <c r="M8" t="n">
-        <v>1310992227.804487</v>
+        <v>1270266654.001233</v>
       </c>
       <c r="N8" t="n">
-        <v>67770179.64749798</v>
+        <v>67770179.58333333</v>
       </c>
     </row>
     <row r="9">
@@ -819,7 +819,7 @@
         <v>44926</v>
       </c>
       <c r="B9" t="n">
-        <v>1122769581.799137</v>
+        <v>1226873116.30141</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -828,7 +828,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>786025802.1002041</v>
+        <v>788465847.702381</v>
       </c>
       <c r="F9" t="n">
         <v>550000000</v>
@@ -843,7 +843,7 @@
         <v>26256250</v>
       </c>
       <c r="J9" t="n">
-        <v>1037500364956001</v>
+        <v>379917205.5251831</v>
       </c>
       <c r="K9" t="n">
         <v>3400000</v>
@@ -852,10 +852,10 @@
         <v>20625000</v>
       </c>
       <c r="M9" t="n">
-        <v>1208395983.88189</v>
+        <v>1167670410.084566</v>
       </c>
       <c r="N9" t="n">
-        <v>1086709580.302703</v>
+        <v>1086709580.204545</v>
       </c>
     </row>
     <row r="10">
@@ -863,7 +863,7 @@
         <v>45016</v>
       </c>
       <c r="B10" t="n">
-        <v>1358795383.938174</v>
+        <v>1489834419.530083</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -872,7 +872,7 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>782317468.7668709</v>
+        <v>784757514.3690476</v>
       </c>
       <c r="F10" t="n">
         <v>1650000000</v>
@@ -887,19 +887,19 @@
         <v>31073026.31578948</v>
       </c>
       <c r="J10" t="n">
-        <v>1037500529782495</v>
+        <v>535806208.5034702</v>
       </c>
       <c r="K10" t="n">
         <v>3400000</v>
       </c>
       <c r="L10" t="n">
-        <v>23923911.54769849</v>
+        <v>23923911.58333333</v>
       </c>
       <c r="M10" t="n">
-        <v>1050044074.251061</v>
+        <v>1009318500.501233</v>
       </c>
       <c r="N10" t="n">
-        <v>102796780.630305</v>
+        <v>102796780.5151515</v>
       </c>
     </row>
     <row r="11">
@@ -907,7 +907,7 @@
         <v>45107</v>
       </c>
       <c r="B11" t="n">
-        <v>1714040042.057832</v>
+        <v>1829498385.233075</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -916,13 +916,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1150158890.851876</v>
+        <v>1152598936.452381</v>
       </c>
       <c r="F11" t="n">
         <v>1650000000</v>
       </c>
       <c r="G11" t="n">
-        <v>71172951.73303618</v>
+        <v>71172951.75</v>
       </c>
       <c r="H11" t="n">
         <v>67625</v>
@@ -931,19 +931,19 @@
         <v>25956578.94736842</v>
       </c>
       <c r="J11" t="n">
-        <v>1037500437614501</v>
+        <v>443638214.3574802</v>
       </c>
       <c r="K11" t="n">
         <v>1133333.333333333</v>
       </c>
       <c r="L11" t="n">
-        <v>65990033.9882144</v>
+        <v>65990034.04166666</v>
       </c>
       <c r="M11" t="n">
-        <v>1128152607.405862</v>
+        <v>1340067224.045064</v>
       </c>
       <c r="N11" t="n">
-        <v>245001823.3665239</v>
+        <v>266801801.5151515</v>
       </c>
     </row>
     <row r="12">
@@ -951,7 +951,7 @@
         <v>45199</v>
       </c>
       <c r="B12" t="n">
-        <v>1852077295.360086</v>
+        <v>1936374253.701995</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -960,34 +960,34 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1152965018.561045</v>
+        <v>1155405064.160714</v>
       </c>
       <c r="F12" t="n">
         <v>1650000000</v>
       </c>
       <c r="G12" t="n">
-        <v>71759427.59955427</v>
+        <v>71759427.625</v>
       </c>
       <c r="H12" t="n">
         <v>67625</v>
       </c>
       <c r="I12" t="n">
-        <v>19222448.14026073</v>
+        <v>19222448.11403508</v>
       </c>
       <c r="J12" t="n">
-        <v>1037500432270361</v>
+        <v>459577386.3158135</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>86198367.32154773</v>
+        <v>86198367.375</v>
       </c>
       <c r="M12" t="n">
-        <v>1292958783.001101</v>
+        <v>1263744689.473635</v>
       </c>
       <c r="N12" t="n">
-        <v>326651555.6085449</v>
+        <v>348451533.7651515</v>
       </c>
     </row>
     <row r="13">
@@ -995,7 +995,7 @@
         <v>45291</v>
       </c>
       <c r="B13" t="n">
-        <v>1954662371.472455</v>
+        <v>2035468874.798486</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1004,34 +1004,34 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>894398800.5589068</v>
+        <v>896838846.1488096</v>
       </c>
       <c r="F13" t="n">
         <v>1650000000</v>
       </c>
       <c r="G13" t="n">
-        <v>59259427.59955428</v>
+        <v>59259427.62499999</v>
       </c>
       <c r="H13" t="n">
         <v>67625</v>
       </c>
       <c r="I13" t="n">
-        <v>19809549.40337356</v>
+        <v>19809549.36403508</v>
       </c>
       <c r="J13" t="n">
-        <v>345834144778909.8</v>
+        <v>849325091.2288172</v>
       </c>
       <c r="K13" t="n">
-        <v>43763058.33192163</v>
+        <v>125346391.6666667</v>
       </c>
       <c r="L13" t="n">
-        <v>86198367.32154773</v>
+        <v>86198367.375</v>
       </c>
       <c r="M13" t="n">
-        <v>1697771283.001101</v>
+        <v>1301890522.806969</v>
       </c>
       <c r="N13" t="n">
-        <v>305376812.5658107</v>
+        <v>327176790.75</v>
       </c>
     </row>
     <row r="14">
@@ -1039,7 +1039,7 @@
         <v>45382</v>
       </c>
       <c r="B14" t="n">
-        <v>2411221911.916485</v>
+        <v>2492028415.263398</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1048,34 +1048,34 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>380927577.1691143</v>
+        <v>383367622.75</v>
       </c>
       <c r="F14" t="n">
         <v>1804166666.666667</v>
       </c>
       <c r="G14" t="n">
-        <v>142592760.9328876</v>
+        <v>142592760.9583333</v>
       </c>
       <c r="H14" t="n">
         <v>67625</v>
       </c>
       <c r="I14" t="n">
-        <v>21192882.73670689</v>
+        <v>21192882.69736842</v>
       </c>
       <c r="J14" t="n">
-        <v>602410379.140847</v>
+        <v>640255310.263158</v>
       </c>
       <c r="K14" t="n">
-        <v>254144587.4978824</v>
+        <v>254019587.5</v>
       </c>
       <c r="L14" t="n">
-        <v>86198367.32154773</v>
+        <v>86198367.375</v>
       </c>
       <c r="M14" t="n">
-        <v>2434864154.38394</v>
+        <v>2345831878.84593</v>
       </c>
       <c r="N14" t="n">
-        <v>304668805.698346</v>
+        <v>326468783.9166667</v>
       </c>
     </row>
     <row r="15">
@@ -1083,7 +1083,7 @@
         <v>45473</v>
       </c>
       <c r="B15" t="n">
-        <v>2632791155.822711</v>
+        <v>2713597659.180065</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -1092,34 +1092,34 @@
         <v>10416666.66666667</v>
       </c>
       <c r="E15" t="n">
-        <v>376250002.3980815</v>
+        <v>378690048</v>
       </c>
       <c r="F15" t="n">
-        <v>6851428926.441351</v>
+        <v>6851428926.5</v>
       </c>
       <c r="G15" t="n">
-        <v>154259427.5995543</v>
+        <v>154259427.625</v>
       </c>
       <c r="H15" t="n">
         <v>67625</v>
       </c>
       <c r="I15" t="n">
-        <v>21192882.73670689</v>
+        <v>21192882.69736842</v>
       </c>
       <c r="J15" t="n">
-        <v>311602703.554067</v>
+        <v>349447635.0250627</v>
       </c>
       <c r="K15" t="n">
-        <v>375965547.719928</v>
+        <v>375840547.75</v>
       </c>
       <c r="L15" t="n">
-        <v>111198367.3215477</v>
+        <v>111198367.375</v>
       </c>
       <c r="M15" t="n">
-        <v>1290369653.928419</v>
+        <v>1504201014.946408</v>
       </c>
       <c r="N15" t="n">
-        <v>332504857.9930602</v>
+        <v>354304836.25</v>
       </c>
     </row>
     <row r="16">
@@ -1127,7 +1127,7 @@
         <v>45565</v>
       </c>
       <c r="B16" t="n">
-        <v>2615085294.978399</v>
+        <v>2547903149.025303</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -1139,31 +1139,31 @@
         <v>3735250000</v>
       </c>
       <c r="F16" t="n">
-        <v>6851428926.441351</v>
+        <v>6851428926.5</v>
       </c>
       <c r="G16" t="n">
-        <v>154259427.5995543</v>
+        <v>154259427.625</v>
       </c>
       <c r="H16" t="n">
         <v>67625</v>
       </c>
       <c r="I16" t="n">
-        <v>21192882.73670689</v>
+        <v>21192882.69736842</v>
       </c>
       <c r="J16" t="n">
-        <v>355413227.0276201</v>
+        <v>395358156.4000627</v>
       </c>
       <c r="K16" t="n">
-        <v>961876027.8309506</v>
+        <v>961751027.8750001</v>
       </c>
       <c r="L16" t="n">
-        <v>112667335.3714927</v>
+        <v>112667335.4166667</v>
       </c>
       <c r="M16" t="n">
-        <v>969536320.5950854</v>
+        <v>908367681.6130748</v>
       </c>
       <c r="N16" t="n">
-        <v>309004857.9930602</v>
+        <v>330804836.25</v>
       </c>
     </row>
     <row r="17">
@@ -1171,7 +1171,7 @@
         <v>45657</v>
       </c>
       <c r="B17" t="n">
-        <v>2514873558.600366</v>
+        <v>2373697088.029444</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -1183,31 +1183,31 @@
         <v>2740833333.333333</v>
       </c>
       <c r="F17" t="n">
-        <v>6902441030.825134</v>
+        <v>6902441030.875</v>
       </c>
       <c r="G17" t="n">
-        <v>154259427.5995543</v>
+        <v>154259427.625</v>
       </c>
       <c r="H17" t="n">
         <v>45083.33333333334</v>
       </c>
       <c r="I17" t="n">
-        <v>5561303.789338471</v>
+        <v>5561303.75</v>
       </c>
       <c r="J17" t="n">
-        <v>362169855.3517003</v>
+        <v>400394817.1369048</v>
       </c>
       <c r="K17" t="n">
-        <v>961876027.8309506</v>
+        <v>961751027.8750001</v>
       </c>
       <c r="L17" t="n">
-        <v>115605271.4713825</v>
+        <v>115605271.5</v>
       </c>
       <c r="M17" t="n">
-        <v>757944984.3093493</v>
+        <v>694409481.4160827</v>
       </c>
       <c r="N17" t="n">
-        <v>247712906.9590676</v>
+        <v>269512885.25</v>
       </c>
     </row>
     <row r="18">
@@ -1215,7 +1215,7 @@
         <v>45747</v>
       </c>
       <c r="B18" t="n">
-        <v>2806865665.150026</v>
+        <v>2630517715.507705</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
@@ -1227,31 +1227,31 @@
         <v>905833333.3333334</v>
       </c>
       <c r="F18" t="n">
-        <v>5802441030.825134</v>
+        <v>5802441030.875</v>
       </c>
       <c r="G18" t="n">
-        <v>135926094.2662209</v>
+        <v>135926094.2916667</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5561303.789338471</v>
+        <v>5561303.75</v>
       </c>
       <c r="J18" t="n">
-        <v>254657086.0600336</v>
+        <v>292882047.8452381</v>
       </c>
       <c r="K18" t="n">
-        <v>961876027.8309506</v>
+        <v>961751027.8750001</v>
       </c>
       <c r="L18" t="n">
-        <v>112306359.923684</v>
+        <v>112306359.9166667</v>
       </c>
       <c r="M18" t="n">
-        <v>1178923439.536053</v>
+        <v>1110654208.772099</v>
       </c>
       <c r="N18" t="n">
-        <v>248480523.1087379</v>
+        <v>270280501.4166667</v>
       </c>
     </row>
     <row r="19">
@@ -1259,7 +1259,7 @@
         <v>45838</v>
       </c>
       <c r="B19" t="n">
-        <v>3031844218.579053</v>
+        <v>2855496268.936732</v>
       </c>
       <c r="C19" t="n">
         <v>11875000</v>
@@ -1271,31 +1271,31 @@
         <v>533750000</v>
       </c>
       <c r="F19" t="n">
-        <v>5802441030.825134</v>
+        <v>5802441030.875</v>
       </c>
       <c r="G19" t="n">
-        <v>125586475.8665181</v>
+        <v>125586475.875</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5561303.789338471</v>
+        <v>5561303.75</v>
       </c>
       <c r="J19" t="n">
-        <v>2676155457.833843</v>
+        <v>2714380419.619048</v>
       </c>
       <c r="K19" t="n">
-        <v>1003542694.497617</v>
+        <v>961751027.8750001</v>
       </c>
       <c r="L19" t="n">
-        <v>56490237.48316807</v>
+        <v>56490237.45833333</v>
       </c>
       <c r="M19" t="n">
-        <v>405902486.082996</v>
+        <v>337633255.3137652</v>
       </c>
       <c r="N19" t="n">
-        <v>299412872.1920713</v>
+        <v>299412872.25</v>
       </c>
     </row>
     <row r="20">
@@ -1303,7 +1303,7 @@
         <v>45930</v>
       </c>
       <c r="B20" t="n">
-        <v>3001336174.813221</v>
+        <v>2872047048.700312</v>
       </c>
       <c r="C20" t="n">
         <v>19375000</v>
@@ -1315,7 +1315,7 @@
         <v>533750000</v>
       </c>
       <c r="F20" t="n">
-        <v>5802441030.825134</v>
+        <v>5802441030.875</v>
       </c>
       <c r="G20" t="n">
         <v>125000000</v>
@@ -1324,22 +1324,22 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3420434.596446157</v>
+        <v>3420434.583333333</v>
       </c>
       <c r="J20" t="n">
-        <v>2654024387.712326</v>
+        <v>2670966037.458333</v>
       </c>
       <c r="K20" t="n">
-        <v>1026667694.497617</v>
+        <v>964042694.5416667</v>
       </c>
       <c r="L20" t="n">
-        <v>29406904.14983474</v>
+        <v>29406904.125</v>
       </c>
       <c r="M20" t="n">
-        <v>4343242830.634278</v>
+        <v>4372730010.121457</v>
       </c>
       <c r="N20" t="n">
-        <v>68835628.44207132</v>
+        <v>68835628.5</v>
       </c>
     </row>
     <row r="21">
@@ -1347,7 +1347,7 @@
         <v>46022</v>
       </c>
       <c r="B21" t="n">
-        <v>2672556095.613041</v>
+        <v>2637384616.5</v>
       </c>
       <c r="C21" t="n">
         <v>19375000</v>
@@ -1359,7 +1359,7 @@
         <v>533750000</v>
       </c>
       <c r="F21" t="n">
-        <v>5802441030.825134</v>
+        <v>5802441030.875</v>
       </c>
       <c r="G21" t="n">
         <v>125000000</v>
@@ -1371,19 +1371,19 @@
         <v>2350000</v>
       </c>
       <c r="J21" t="n">
-        <v>2623734560.420659</v>
+        <v>2630034554.125</v>
       </c>
       <c r="K21" t="n">
-        <v>987487969.499029</v>
+        <v>843279636.2083334</v>
       </c>
       <c r="L21" t="n">
-        <v>29406904.14983474</v>
+        <v>29406904.125</v>
       </c>
       <c r="M21" t="n">
-        <v>196052631.5789474</v>
+        <v>212719298.2456141</v>
       </c>
       <c r="N21" t="n">
-        <v>68831878.44207132</v>
+        <v>68831878.5</v>
       </c>
     </row>
   </sheetData>

--- a/reconcile/storage/output/ongoing/ongoing_total_q.xlsx
+++ b/reconcile/storage/output/ongoing/ongoing_total_q.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N21"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,60 +447,70 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>cement</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>geothermal</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>hydroelectric</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>hydrogen</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>iron</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>nuclear</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>parts</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>powertrain</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>recycling</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>solar</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>steel</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>unclear</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>vehicle</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>wind</t>
         </is>
@@ -508,10 +518,10 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>44286</v>
+        <v>42825</v>
       </c>
       <c r="B2" t="n">
-        <v>975632004.4959705</v>
+        <v>162462626.5714286</v>
       </c>
       <c r="C2" t="n">
         <v>0</v>
@@ -520,7 +530,7 @@
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>20609166.66666667</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -532,10 +542,10 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>11550679</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>230695539.1742424</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -544,18 +554,24 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1089716321.471411</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>46959256.25</v>
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>231336743.4007936</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>44377</v>
+        <v>42916</v>
       </c>
       <c r="B3" t="n">
-        <v>1203405117.125172</v>
+        <v>91335161.23809524</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -564,7 +580,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>102267744.5833333</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -576,30 +592,36 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>14750000</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>320960111.2992424</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>2266666.666666667</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13750000</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1171530676.554744</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>39657062.33333334</v>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>196591846.5119047</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>44469</v>
+        <v>43008</v>
       </c>
       <c r="B4" t="n">
-        <v>1226935668.625172</v>
+        <v>55771428.57142857</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
@@ -608,7 +630,7 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>21961616.875</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -620,30 +642,36 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>23625000</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>286982974.0730519</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>20625000</v>
+        <v>446666.6666666667</v>
       </c>
       <c r="M4" t="n">
-        <v>1323440636.721411</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>59943623.83333334</v>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>207015238.0952381</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>44561</v>
+        <v>43100</v>
       </c>
       <c r="B5" t="n">
-        <v>1229672233.833505</v>
+        <v>163026511.3214286</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -652,42 +680,48 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>206099263.4583333</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>12500000</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>24895833.33333334</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>141221908.3641775</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K5" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>20625000</v>
+        <v>670000</v>
       </c>
       <c r="M5" t="n">
-        <v>1193037557.011266</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>76853757</v>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>271181904.7619047</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>44651</v>
+        <v>43190</v>
       </c>
       <c r="B6" t="n">
-        <v>879782009.4745311</v>
+        <v>206573530.9929972</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -696,42 +730,48 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>570251677.3333334</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>12500000</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>26256250</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>288637021.4285715</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K6" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>20625000</v>
+        <v>26185597.01666667</v>
       </c>
       <c r="M6" t="n">
-        <v>1651606397.590976</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>89171252.5</v>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>298681904.7619047</v>
+      </c>
+      <c r="P6" t="n">
+        <v>27500</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>44742</v>
+        <v>43281</v>
       </c>
       <c r="B7" t="n">
-        <v>1158727522.295044</v>
+        <v>241273651.6694678</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -740,42 +780,48 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>618323418.75</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>42500000</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>26256250</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>294395616.4285714</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>20625000</v>
+        <v>43187958.21111111</v>
       </c>
       <c r="M7" t="n">
-        <v>1219257038.616617</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>75513700.41666667</v>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>298681904.7619047</v>
+      </c>
+      <c r="P7" t="n">
+        <v>138287.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>44834</v>
+        <v>43373</v>
       </c>
       <c r="B8" t="n">
-        <v>1282575462.589161</v>
+        <v>252386796.39169</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -784,42 +830,48 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>573763466.75</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>662500000</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>26256250</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>752594557.5535715</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>20625000</v>
+        <v>59770107.41578947</v>
       </c>
       <c r="M8" t="n">
-        <v>1270266654.001233</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>67770179.58333333</v>
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>313482738.0952381</v>
+      </c>
+      <c r="P8" t="n">
+        <v>174254.1666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>44926</v>
+        <v>43465</v>
       </c>
       <c r="B9" t="n">
-        <v>1226873116.30141</v>
+        <v>569686229.3617754</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -828,42 +880,48 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>788465847.702381</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>550000000</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>42500000</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>22541.66666666667</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>26256250</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>379917205.5251831</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K9" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>20625000</v>
+        <v>74975172.24035087</v>
       </c>
       <c r="M9" t="n">
-        <v>1167670410.084566</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1086709580.204545</v>
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>416390194.235589</v>
+      </c>
+      <c r="P9" t="n">
+        <v>3041337.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>45016</v>
+        <v>43555</v>
       </c>
       <c r="B10" t="n">
-        <v>1489834419.530083</v>
+        <v>510329028.230823</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -872,42 +930,48 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>784757514.3690476</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1650000000</v>
+        <v>141111.1111111111</v>
       </c>
       <c r="G10" t="n">
-        <v>60833333.33333333</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>31073026.31578948</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>535806208.5034702</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K10" t="n">
-        <v>3400000</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23923911.58333333</v>
+        <v>76010100.57368422</v>
       </c>
       <c r="M10" t="n">
-        <v>1009318500.501233</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>102796780.5151515</v>
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>516214755.6390977</v>
+      </c>
+      <c r="P10" t="n">
+        <v>4480712.5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>45107</v>
+        <v>43646</v>
       </c>
       <c r="B11" t="n">
-        <v>1829498385.233075</v>
+        <v>502819107.5959024</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -916,42 +980,48 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>1152598936.452381</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1650000000</v>
+        <v>211666.6666666667</v>
       </c>
       <c r="G11" t="n">
-        <v>71172951.75</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>25956578.94736842</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>443638214.3574802</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K11" t="n">
-        <v>1133333.333333333</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>65990034.04166666</v>
+        <v>77450450.57368422</v>
       </c>
       <c r="M11" t="n">
-        <v>1340067224.045064</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>266801801.5151515</v>
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>487624477.86132</v>
+      </c>
+      <c r="P11" t="n">
+        <v>20100136.11111111</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>45199</v>
+        <v>43738</v>
       </c>
       <c r="B12" t="n">
-        <v>1936374253.701995</v>
+        <v>507888552.0403469</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -960,42 +1030,48 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>1155405064.160714</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1650000000</v>
+        <v>211666.6666666667</v>
       </c>
       <c r="G12" t="n">
-        <v>71759427.625</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>19222448.11403508</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>459577386.3158135</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>86198367.375</v>
+        <v>77471065.57368422</v>
       </c>
       <c r="M12" t="n">
-        <v>1263744689.473635</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>348451533.7651515</v>
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>833845071.7640977</v>
+      </c>
+      <c r="P12" t="n">
+        <v>30124594.44444445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>45291</v>
+        <v>43830</v>
       </c>
       <c r="B13" t="n">
-        <v>2035468874.798486</v>
+        <v>931556370.8124057</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1004,42 +1080,48 @@
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>896838846.1488096</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>1650000000</v>
+        <v>211666.6666666667</v>
       </c>
       <c r="G13" t="n">
-        <v>59259427.62499999</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>19809549.36403508</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>849325091.2288172</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K13" t="n">
-        <v>125346391.6666667</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>86198367.375</v>
+        <v>161794159.4625731</v>
       </c>
       <c r="M13" t="n">
-        <v>1301890522.806969</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>327176790.75</v>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>877694331.5855263</v>
+      </c>
+      <c r="P13" t="n">
+        <v>31312658.33333333</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>45382</v>
+        <v>43921</v>
       </c>
       <c r="B14" t="n">
-        <v>2492028415.263398</v>
+        <v>969758985.1914907</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
@@ -1048,342 +1130,1140 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>383367622.75</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>1804166666.666667</v>
+        <v>4378333.333333333</v>
       </c>
       <c r="G14" t="n">
-        <v>142592760.9583333</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>21192882.69736842</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>640255310.263158</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K14" t="n">
-        <v>254019587.5</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>86198367.375</v>
+        <v>173008364.6380117</v>
       </c>
       <c r="M14" t="n">
-        <v>2345831878.84593</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>326468783.9166667</v>
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>1484184348.417486</v>
+      </c>
+      <c r="P14" t="n">
+        <v>31934121.05555555</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>45473</v>
+        <v>44012</v>
       </c>
       <c r="B15" t="n">
-        <v>2713597659.180065</v>
+        <v>1009318335.691491</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>10416666.66666667</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>378690048</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>6851428926.5</v>
+        <v>12711666.66666667</v>
       </c>
       <c r="G15" t="n">
-        <v>154259427.625</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>21192882.69736842</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>349447635.0250627</v>
+        <v>71428571.42857143</v>
       </c>
       <c r="K15" t="n">
-        <v>375840547.75</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>111198367.375</v>
+        <v>180069362.6</v>
       </c>
       <c r="M15" t="n">
-        <v>1504201014.946408</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>354304836.25</v>
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>1509065812.986199</v>
+      </c>
+      <c r="P15" t="n">
+        <v>33940485.27777778</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>45565</v>
+        <v>44104</v>
       </c>
       <c r="B16" t="n">
-        <v>2547903149.025303</v>
+        <v>1058952463.39784</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>31250000</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>3735250000</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>6851428926.5</v>
+        <v>12711666.66666667</v>
       </c>
       <c r="G16" t="n">
-        <v>154259427.625</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>67625</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>21192882.69736842</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>395358156.4000627</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>961751027.8750001</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>112667335.4166667</v>
+        <v>191175440.4333333</v>
       </c>
       <c r="M16" t="n">
-        <v>908367681.6130748</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>330804836.25</v>
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1512018653.419545</v>
+      </c>
+      <c r="P16" t="n">
+        <v>35505104.5</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>45657</v>
+        <v>44196</v>
       </c>
       <c r="B17" t="n">
-        <v>2373697088.029444</v>
+        <v>1002868033.14784</v>
       </c>
       <c r="C17" t="n">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>31250000</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>2740833333.333333</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>6902441030.875</v>
+        <v>12711666.66666667</v>
       </c>
       <c r="G17" t="n">
-        <v>154259427.625</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>45083.33333333334</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>5561303.75</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>400394817.1369048</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>961751027.8750001</v>
+        <v>322222.2222222222</v>
       </c>
       <c r="L17" t="n">
-        <v>115605271.5</v>
+        <v>196015334.0444444</v>
       </c>
       <c r="M17" t="n">
-        <v>694409481.4160827</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>269512885.25</v>
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>1424039308.757323</v>
+      </c>
+      <c r="P17" t="n">
+        <v>35542867</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>45747</v>
+        <v>44286</v>
       </c>
       <c r="B18" t="n">
-        <v>2630517715.507705</v>
+        <v>1018639099.912637</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>31250000</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>905833333.3333334</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>5802441030.875</v>
+        <v>13739444.44444444</v>
       </c>
       <c r="G18" t="n">
-        <v>135926094.2916667</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>5561303.75</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>292882047.8452381</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>961751027.8750001</v>
+        <v>12517345.66666667</v>
       </c>
       <c r="L18" t="n">
-        <v>112306359.9166667</v>
+        <v>311456333.2992424</v>
       </c>
       <c r="M18" t="n">
-        <v>1110654208.772099</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>270280501.4166667</v>
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1230659984.512243</v>
+      </c>
+      <c r="P18" t="n">
+        <v>37357725.33333334</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>45838</v>
+        <v>44377</v>
       </c>
       <c r="B19" t="n">
-        <v>2855496268.936732</v>
+        <v>1236569142.875172</v>
       </c>
       <c r="C19" t="n">
-        <v>11875000</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>31250000</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>533750000</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>5802441030.875</v>
+        <v>95011829.72222222</v>
       </c>
       <c r="G19" t="n">
-        <v>125586475.875</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>5561303.75</v>
+        <v>20000000</v>
       </c>
       <c r="J19" t="n">
-        <v>2714380419.619048</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>961751027.8750001</v>
+        <v>10800000</v>
       </c>
       <c r="L19" t="n">
-        <v>56490237.45833333</v>
+        <v>374612360.854798</v>
       </c>
       <c r="M19" t="n">
-        <v>337633255.3137652</v>
+        <v>1511111.111111111</v>
       </c>
       <c r="N19" t="n">
-        <v>299412872.25</v>
+        <v>9166666.666666666</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1246533000.385259</v>
+      </c>
+      <c r="P19" t="n">
+        <v>38163604.5</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>45930</v>
+        <v>44469</v>
       </c>
       <c r="B20" t="n">
-        <v>2872047048.700312</v>
+        <v>1229618031.764061</v>
       </c>
       <c r="C20" t="n">
-        <v>19375000</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>31250000</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>533750000</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>5802441030.875</v>
+        <v>14641077.91666666</v>
       </c>
       <c r="G20" t="n">
-        <v>125000000</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>3420434.583333333</v>
+        <v>20000000</v>
       </c>
       <c r="J20" t="n">
-        <v>2670966037.458333</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>964042694.5416667</v>
+        <v>16716666.66666667</v>
       </c>
       <c r="L20" t="n">
-        <v>29406904.125</v>
+        <v>311392830.8230519</v>
       </c>
       <c r="M20" t="n">
-        <v>4372730010.121457</v>
+        <v>2266666.666666667</v>
       </c>
       <c r="N20" t="n">
-        <v>68835628.5</v>
+        <v>13750000</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1473411028.243845</v>
+      </c>
+      <c r="P20" t="n">
+        <v>52902692.94444445</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46022</v>
+        <v>44561</v>
       </c>
       <c r="B21" t="n">
-        <v>2637384616.5</v>
+        <v>1140514575.625172</v>
       </c>
       <c r="C21" t="n">
-        <v>19375000</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>31250000</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>533750000</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>5802441030.875</v>
+        <v>137399508.9722222</v>
       </c>
       <c r="G21" t="n">
-        <v>125000000</v>
+        <v>61111111.11111111</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>366666666.6666667</v>
       </c>
       <c r="I21" t="n">
-        <v>2350000</v>
+        <v>28333333.33333333</v>
       </c>
       <c r="J21" t="n">
-        <v>2630034554.125</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>843279636.2083334</v>
+        <v>17504166.66666666</v>
       </c>
       <c r="L21" t="n">
-        <v>29406904.125</v>
+        <v>308024344.7530664</v>
       </c>
       <c r="M21" t="n">
-        <v>212719298.2456141</v>
+        <v>2266666.666666667</v>
       </c>
       <c r="N21" t="n">
-        <v>68831878.5</v>
+        <v>13750000</v>
+      </c>
+      <c r="O21" t="n">
+        <v>1793805869.513686</v>
+      </c>
+      <c r="P21" t="n">
+        <v>64155672</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>44651</v>
+      </c>
+      <c r="B22" t="n">
+        <v>808374351.2661978</v>
+      </c>
+      <c r="C22" t="n">
+        <v>3636363.636363636</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>384334451.5555555</v>
+      </c>
+      <c r="G22" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I22" t="n">
+        <v>40555555.55555555</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>17897916.66666666</v>
+      </c>
+      <c r="L22" t="n">
+        <v>319456732.3869048</v>
+      </c>
+      <c r="M22" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N22" t="n">
+        <v>13750000</v>
+      </c>
+      <c r="O22" t="n">
+        <v>1163641644.849462</v>
+      </c>
+      <c r="P22" t="n">
+        <v>70540935.66666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>44742</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1160876898.13689</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10909090.90909091</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>794548945.8333333</v>
+      </c>
+      <c r="G23" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I23" t="n">
+        <v>47448634.5</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>17897916.66666666</v>
+      </c>
+      <c r="L23" t="n">
+        <v>325523459.609127</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N23" t="n">
+        <v>13750000</v>
+      </c>
+      <c r="O23" t="n">
+        <v>781232337.8424685</v>
+      </c>
+      <c r="P23" t="n">
+        <v>69526212.05555555</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>44834</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1240206827.678319</v>
+      </c>
+      <c r="C24" t="n">
+        <v>10909090.90909091</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>749175644.5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I24" t="n">
+        <v>47839618.41666666</v>
+      </c>
+      <c r="J24" t="n">
+        <v>620000000</v>
+      </c>
+      <c r="K24" t="n">
+        <v>17897916.66666666</v>
+      </c>
+      <c r="L24" t="n">
+        <v>602710911.2619047</v>
+      </c>
+      <c r="M24" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N24" t="n">
+        <v>13750000</v>
+      </c>
+      <c r="O24" t="n">
+        <v>885556753.1361747</v>
+      </c>
+      <c r="P24" t="n">
+        <v>90572176.02614379</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>44926</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1167219759.168345</v>
+      </c>
+      <c r="C25" t="n">
+        <v>10909090.90909091</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>963739136.5634921</v>
+      </c>
+      <c r="G25" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I25" t="n">
+        <v>47839618.41666666</v>
+      </c>
+      <c r="J25" t="n">
+        <v>15027.77777777778</v>
+      </c>
+      <c r="K25" t="n">
+        <v>17897916.66666666</v>
+      </c>
+      <c r="L25" t="n">
+        <v>459158768.3168498</v>
+      </c>
+      <c r="M25" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N25" t="n">
+        <v>13750000</v>
+      </c>
+      <c r="O25" t="n">
+        <v>891394040.3306191</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1103329583.258467</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>45016</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1360206062.397019</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3636363.636363636</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>957128025.4523809</v>
+      </c>
+      <c r="G26" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I26" t="n">
+        <v>47839618.41666666</v>
+      </c>
+      <c r="J26" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K26" t="n">
+        <v>22714692.98245614</v>
+      </c>
+      <c r="L26" t="n">
+        <v>434326337.9201369</v>
+      </c>
+      <c r="M26" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N26" t="n">
+        <v>15949274.38888889</v>
+      </c>
+      <c r="O26" t="n">
+        <v>964412554.8930435</v>
+      </c>
+      <c r="P26" t="n">
+        <v>113511635.2635175</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>45107</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1494771925.572232</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>942794692.1190476</v>
+      </c>
+      <c r="G27" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I27" t="n">
+        <v>47839618.41666666</v>
+      </c>
+      <c r="J27" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K27" t="n">
+        <v>32348245.61403509</v>
+      </c>
+      <c r="L27" t="n">
+        <v>324261338.7463691</v>
+      </c>
+      <c r="M27" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N27" t="n">
+        <v>53160022.69444444</v>
+      </c>
+      <c r="O27" t="n">
+        <v>1156640645.119955</v>
+      </c>
+      <c r="P27" t="n">
+        <v>202542382.1524064</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>45199</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1553557498.076506</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>945794692.1190476</v>
+      </c>
+      <c r="G28" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I28" t="n">
+        <v>47839618.41666666</v>
+      </c>
+      <c r="J28" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K28" t="n">
+        <v>33775491.7251462</v>
+      </c>
+      <c r="L28" t="n">
+        <v>645667924.8019247</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2266666.666666667</v>
+      </c>
+      <c r="N28" t="n">
+        <v>71215578.25</v>
+      </c>
+      <c r="O28" t="n">
+        <v>1228085942.450488</v>
+      </c>
+      <c r="P28" t="n">
+        <v>269419568.4857397</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>45291</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1762114546.25633</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>871366120.6904762</v>
+      </c>
+      <c r="G29" t="n">
+        <v>91666666.66666667</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1100000000</v>
+      </c>
+      <c r="I29" t="n">
+        <v>47839618.41666666</v>
+      </c>
+      <c r="J29" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K29" t="n">
+        <v>34166892.55847953</v>
+      </c>
+      <c r="L29" t="n">
+        <v>726436090.4093728</v>
+      </c>
+      <c r="M29" t="n">
+        <v>85830927.77777778</v>
+      </c>
+      <c r="N29" t="n">
+        <v>71215578.25</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1352544275.783821</v>
+      </c>
+      <c r="P29" t="n">
+        <v>269391321.1372549</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>45382</v>
+      </c>
+      <c r="B30" t="n">
+        <v>2089294590.776798</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>727481200.0555556</v>
+      </c>
+      <c r="G30" t="n">
+        <v>92333333.33333334</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1202777777.777778</v>
+      </c>
+      <c r="I30" t="n">
+        <v>103395173.9722222</v>
+      </c>
+      <c r="J30" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K30" t="n">
+        <v>35089114.78070175</v>
+      </c>
+      <c r="L30" t="n">
+        <v>556103868.6798246</v>
+      </c>
+      <c r="M30" t="n">
+        <v>170946391.6666667</v>
+      </c>
+      <c r="N30" t="n">
+        <v>71215578.25</v>
+      </c>
+      <c r="O30" t="n">
+        <v>1544068085.307631</v>
+      </c>
+      <c r="P30" t="n">
+        <v>276448330.248366</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>45473</v>
+      </c>
+      <c r="B31" t="n">
+        <v>2239507420.054576</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>6944444.444444444</v>
+      </c>
+      <c r="F31" t="n">
+        <v>726708814.7777778</v>
+      </c>
+      <c r="G31" t="n">
+        <v>92333333.33333334</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4567619284.333333</v>
+      </c>
+      <c r="I31" t="n">
+        <v>111172951.75</v>
+      </c>
+      <c r="J31" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K31" t="n">
+        <v>25255781.44736842</v>
+      </c>
+      <c r="L31" t="n">
+        <v>268302944.2750627</v>
+      </c>
+      <c r="M31" t="n">
+        <v>367315920.7222222</v>
+      </c>
+      <c r="N31" t="n">
+        <v>78715578.25</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1779448202.266695</v>
+      </c>
+      <c r="P31" t="n">
+        <v>295005698.4705882</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>45565</v>
+      </c>
+      <c r="B32" t="n">
+        <v>2154788196.872037</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>20833333.33333333</v>
+      </c>
+      <c r="F32" t="n">
+        <v>3910579566.583333</v>
+      </c>
+      <c r="G32" t="n">
+        <v>92333333.33333334</v>
+      </c>
+      <c r="H32" t="n">
+        <v>4567619284.333333</v>
+      </c>
+      <c r="I32" t="n">
+        <v>111172951.75</v>
+      </c>
+      <c r="J32" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K32" t="n">
+        <v>19339114.78070175</v>
+      </c>
+      <c r="L32" t="n">
+        <v>302934780.7472849</v>
+      </c>
+      <c r="M32" t="n">
+        <v>640500685.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>75111556.94444445</v>
+      </c>
+      <c r="O32" t="n">
+        <v>1675992986.847194</v>
+      </c>
+      <c r="P32" t="n">
+        <v>259735310.0261438</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>45657</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1868152213.878865</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>20833333.33333333</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2793821135.527778</v>
+      </c>
+      <c r="G33" t="n">
+        <v>31222222.22222222</v>
+      </c>
+      <c r="H33" t="n">
+        <v>4601627353.916667</v>
+      </c>
+      <c r="I33" t="n">
+        <v>102839618.4166667</v>
+      </c>
+      <c r="J33" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3707535.833333333</v>
+      </c>
+      <c r="L33" t="n">
+        <v>350539632.8174603</v>
+      </c>
+      <c r="M33" t="n">
+        <v>640500685.25</v>
+      </c>
+      <c r="N33" t="n">
+        <v>77070181</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1518400183.059012</v>
+      </c>
+      <c r="P33" t="n">
+        <v>204617580.9705882</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>45747</v>
+      </c>
+      <c r="B34" t="n">
+        <v>2109041003.195836</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>20833333.33333333</v>
+      </c>
+      <c r="F34" t="n">
+        <v>710633970.7222222</v>
+      </c>
+      <c r="G34" t="n">
+        <v>666666.6666666666</v>
+      </c>
+      <c r="H34" t="n">
+        <v>3868294020.583333</v>
+      </c>
+      <c r="I34" t="n">
+        <v>90617396.19444445</v>
+      </c>
+      <c r="J34" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3707535.833333333</v>
+      </c>
+      <c r="L34" t="n">
+        <v>275463099.6785714</v>
+      </c>
+      <c r="M34" t="n">
+        <v>640500685.25</v>
+      </c>
+      <c r="N34" t="n">
+        <v>77070181</v>
+      </c>
+      <c r="O34" t="n">
+        <v>1339359184.841543</v>
+      </c>
+      <c r="P34" t="n">
+        <v>207910428.4150327</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2492195061.675368</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7916666.666666667</v>
+      </c>
+      <c r="E35" t="n">
+        <v>20833333.33333333</v>
+      </c>
+      <c r="F35" t="n">
+        <v>358293365.3333333</v>
+      </c>
+      <c r="G35" t="n">
+        <v>666666.6666666666</v>
+      </c>
+      <c r="H35" t="n">
+        <v>3868294020.583333</v>
+      </c>
+      <c r="I35" t="n">
+        <v>83724317.25</v>
+      </c>
+      <c r="J35" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3707535.833333333</v>
+      </c>
+      <c r="L35" t="n">
+        <v>267964632.8134921</v>
+      </c>
+      <c r="M35" t="n">
+        <v>640500685.25</v>
+      </c>
+      <c r="N35" t="n">
+        <v>77070181</v>
+      </c>
+      <c r="O35" t="n">
+        <v>1379407795.952654</v>
+      </c>
+      <c r="P35" t="n">
+        <v>324632891.3235294</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="B36" t="n">
+        <v>2318422482.85309</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>12916666.66666667</v>
+      </c>
+      <c r="E36" t="n">
+        <v>20833333.33333333</v>
+      </c>
+      <c r="F36" t="n">
+        <v>356666666.6666667</v>
+      </c>
+      <c r="G36" t="n">
+        <v>666666.6666666666</v>
+      </c>
+      <c r="H36" t="n">
+        <v>3868294020.583333</v>
+      </c>
+      <c r="I36" t="n">
+        <v>83333333.33333333</v>
+      </c>
+      <c r="J36" t="n">
+        <v>45083.33333333333</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3707535.833333333</v>
+      </c>
+      <c r="L36" t="n">
+        <v>245603072.1666667</v>
+      </c>
+      <c r="M36" t="n">
+        <v>640500685.25</v>
+      </c>
+      <c r="N36" t="n">
+        <v>77070181</v>
+      </c>
+      <c r="O36" t="n">
+        <v>1291644040.149235</v>
+      </c>
+      <c r="P36" t="n">
+        <v>167983086.6666667</v>
       </c>
     </row>
   </sheetData>
